--- a/public/exports/29188416.xlsx
+++ b/public/exports/29188416.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">719011, 2293830</t>
+          <t xml:space="preserve">719015, 2293827</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">719015, 2293827</t>
+          <t xml:space="preserve">8613481</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F19">
-        <v>251</v>
+        <v>451</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -986,11 +986,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F20">
-        <v>451</v>
+        <v>1791</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,30 +1031,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8613481</t>
+          <t xml:space="preserve">2296052</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F21">
-        <v>1791</v>
+        <v>485</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311091647</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-01-19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1081,30 +1081,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">9724887</t>
+          <t xml:space="preserve">2295219</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F22">
-        <v>331</v>
+        <v>470</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311128996</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-08-13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2296052</t>
+          <t xml:space="preserve">2278907</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>485</v>
+        <v>355</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311091647</t>
+          <t xml:space="preserve">311133770</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-19</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295219</t>
+          <t xml:space="preserve">2278907</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F24">
-        <v>470</v>
+        <v>272</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311128996</t>
+          <t xml:space="preserve">311133771</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-13</t>
+          <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278907</t>
+          <t xml:space="preserve">2297884</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F25">
-        <v>355</v>
+        <v>1224</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133770</t>
+          <t xml:space="preserve">311140672</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278907</t>
+          <t xml:space="preserve">2297884</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F26">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133772</t>
+          <t xml:space="preserve">311140672</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-09</t>
+          <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1331,20 +1331,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2297884</t>
+          <t xml:space="preserve">9724887</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F27">
-        <v>1224</v>
+        <v>331</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140672</t>
+          <t xml:space="preserve">311140790</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1381,25 +1381,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2297884</t>
+          <t xml:space="preserve">2295652</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F28">
-        <v>337</v>
+        <v>2396</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140672</t>
+          <t xml:space="preserve">311140987</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-19</t>
+          <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1436,11 +1436,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F29">
-        <v>2396</v>
+        <v>520</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F30">
-        <v>520</v>
+        <v>1111</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1536,11 +1536,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F31">
-        <v>1111</v>
+        <v>1044</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,20 +1581,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295652</t>
+          <t xml:space="preserve">9162566</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>1044</v>
+        <v>274</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140987</t>
+          <t xml:space="preserve">311141202</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1636,15 +1636,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F33">
-        <v>274</v>
+        <v>494</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141202</t>
+          <t xml:space="preserve">311141205</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1686,20 +1686,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>494</v>
+        <v>1137</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141205</t>
+          <t xml:space="preserve">311142216</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-21</t>
+          <t xml:space="preserve">2025-10-28</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162566</t>
+          <t xml:space="preserve">8613481</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>1137</v>
+        <v>345</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311142216</t>
+          <t xml:space="preserve">311143453</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-28</t>
+          <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F36">
-        <v>345</v>
+        <v>1518</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F37">
-        <v>1518</v>
+        <v>842</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F38">
-        <v>842</v>
+        <v>1424</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1936,15 +1936,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F39">
-        <v>1424</v>
+        <v>342</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143453</t>
+          <t xml:space="preserve">311143454</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8613481</t>
+          <t xml:space="preserve">9122664</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F40">
-        <v>342</v>
+        <v>558</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143454</t>
+          <t xml:space="preserve">311161707</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-04</t>
+          <t xml:space="preserve">2026-03-01</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,35 +2031,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">9122664</t>
+          <t xml:space="preserve">7807845</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>558</v>
+        <v>349</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311161707</t>
+          <t xml:space="preserve">311372721</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-01</t>
+          <t xml:space="preserve">2029-04-24</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7807845</t>
+          <t xml:space="preserve">8727345</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="F42">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372721</t>
+          <t xml:space="preserve">311372706</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727345</t>
+          <t xml:space="preserve">719011, 2293830</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,16 +2140,16 @@
         </is>
       </c>
       <c r="F43">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372706</t>
+          <t xml:space="preserve">311412486</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-24</t>
+          <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9122632</t>
+          <t xml:space="preserve">8562604</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>5573</v>
+        <v>685</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710610</t>
+          <t xml:space="preserve">311718496</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-27</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562604</t>
+          <t xml:space="preserve">9122632</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,11 +2540,11 @@
         </is>
       </c>
       <c r="F51">
-        <v>685</v>
+        <v>5573</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718496</t>
+          <t xml:space="preserve">311718453</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">

--- a/public/exports/29188416.xlsx
+++ b/public/exports/29188416.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:L106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 87</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100584098</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>831</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ebbedal 14C</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10185333</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>357</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sportsvej 7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">10185333</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1112</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sportsvej 5C</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">10185333</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1918</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovfogedlodden 5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2278774</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>384</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sportsvej 5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2278974</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>2304</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skåninggårdsvej 34</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2279835</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>447</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lynæs Havnevej 3A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2293833</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>273</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbjergvej 1A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>453</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bellisvej 43</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2298768</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>267</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkegade 14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317091</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>348</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 55A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318215, 100190403</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>612</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krudtværksalleen 13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318232</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>485</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krudtværksalleen 10</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318242</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>486</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 51B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">718961, 9641311</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>706</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lynæs Havnevej 13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">719006, 2293825</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>439</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lynæs Havnevej 15B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">719015, 2293827</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>251</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>451</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>1791</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 40</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>485</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311091647</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-01-19</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 81A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295219</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>470</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311128996</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-08-13</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sonnerupvej 5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2278907</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>355</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311133770</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311133771</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sonnerupvej 5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2278907</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>272</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311133771</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2297884</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1224</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311140672</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2297884</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>337</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311140672</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 150</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">9724887</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>331</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311140790</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 87</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295652</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>2396</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311140987</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 85</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295652</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>520</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311140987</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 87</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295652</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>1111</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311140987</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 87</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295652</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>1044</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311140987</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 17</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">9162566</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>274</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311141202</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 19</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">9162566</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>494</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311141205</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">9162566</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>1137</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311142216</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-10-28</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>345</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311143453</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1518</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311143453</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>842</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311143453</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134B</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1424</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311143453</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 134A</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">8613481</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>342</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311143454</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnesvinget 10</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">9122664</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>558</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311161707</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-01</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 11B</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">7807845</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>349</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311372721</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-04-24</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højbjerggårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">8727345</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>391</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311372706</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-04-24</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lynæs Havnevej 3D</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">719011, 2293830</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>367</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311412486</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2297884</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>6634</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311626030</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndergade 81A</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295219</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>2857</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311642676</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gasværksvej 13</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295206</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>487</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311674352</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gasværksvej 37</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295206</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>348</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311674352</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Melbyvej 150</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">9724887</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>682</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311703721</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-30</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gjethusparken 4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317133</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>475</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311705730</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-09-07</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ølstedvej 24</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">8562604</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>685</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311718496</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">9122632</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>5573</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311718453</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">9122632</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>2042</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311719517</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-02</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valseværksstræde 5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">9122646</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>570</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311723451</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvet 20</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317120</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>330</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311724031</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tollerupvej 27B</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2282924</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>512</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311725338</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 10F</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317079</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>373</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311725903</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jernbanegade 2A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317772</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>1464</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311726230</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jernbanegade 2B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317772</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>1125</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311726230</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstebrovej 14</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">9068854</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>766</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311727252</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Karlsgavevej 1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2278774</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>7950</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311780833</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solhjemsvej 7</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3370</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2287251</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>3030</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311780834</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klokkedybet 2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">9746735</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>321</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311780835</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klokkedybet 12</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">9746735</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>321</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311780835</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klokkedybet 22</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">9746735</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>321</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311780835</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klokkedybet 32</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">9746735</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>321</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311780835</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Klokkedybet 52</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">9746735</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>5707</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311780836</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bavnager 1A</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">9773051</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>2154</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311780838</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstesvinget 3</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">100012416</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>1337</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311796292</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krudtværksvej 3</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">100034041</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>2033</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311796290</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 47</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2290583</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>254</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311796289</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkevej 10</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295665</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>411</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311796287</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkevej 10</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2295665</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1601</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311796286</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 25</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2300534</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>694</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311796281</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gjethusgade 5</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317131</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>2198</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311796293</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vognmandsgade 12</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317134</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>582</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311796296</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vognmandsgade 14</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317134</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>452</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311796296</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krudtværksalleen 7</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318229</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>325</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311796291</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahornvej 1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318273</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>635</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311796294</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spodsbjergvej 4</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">8261705</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1025</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311796282</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovfogedlodden 10</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2278775</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>702</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311803332</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skåninggårdsvej 32</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2279835</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>722</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311803330</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 61</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2290025</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>807</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311803323</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørregade 61</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2290025</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>672</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311803323</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tømrergade 3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2290025</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>594</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311803337</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>792</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311803328</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>3658</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311803328</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>1012</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311803328</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>1012</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311803328</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>1629</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311803327</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Baggersvej 17</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2298882</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>920</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311803329</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 19A</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318223</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>905</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311803333</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 41A</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318230</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>588</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311803334</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Birkedommeralle 6A</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318254</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>2110</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311803335</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højmarksvej 1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">100062310</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>2275</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311867645</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 42</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2296052</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>2659</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311867648</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318150</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>1447</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311867643</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 4</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318150</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>700</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311867644</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syrevej 6E</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318155</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>572</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311867646</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jonnasvej 4</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3360</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2284212</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>538</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311869855</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Baggersvej 19A</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2298265</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>644</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311869857</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 1A</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3310</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2300568</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>472</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311869854</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvet 41</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">5317128</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>2563</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311869858</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parallelvej 12</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3390</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2290424</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>254</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311873155</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhuspladsen 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">5318150</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>5652</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311873156</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sportsvej 15</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2279001</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>14115</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311874692</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,39 +6331,49 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2297884</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>1564</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311922832</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:L106"/>
 </worksheet>
 </file>
--- a/public/exports/29188416.xlsx
+++ b/public/exports/29188416.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 87</t>
+          <t xml:space="preserve">Bellisvej 43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100584098</t>
+          <t xml:space="preserve">2298768</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>831</v>
+        <v>267</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 7</t>
+          <t xml:space="preserve">Kirkegade 14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10185333</t>
+          <t xml:space="preserve">5317091</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>1112</v>
+        <v>348</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 5C</t>
+          <t xml:space="preserve">Krudtværksalleen 10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10185333</t>
+          <t xml:space="preserve">5318242</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H5">
-        <v>1918</v>
+        <v>486</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovfogedlodden 5</t>
+          <t xml:space="preserve">Krudtværksalleen 13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278774</t>
+          <t xml:space="preserve">5318232</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H6">
-        <v>384</v>
+        <v>485</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 5</t>
+          <t xml:space="preserve">Lerbjergvej 1A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278974</t>
+          <t xml:space="preserve">2296052</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H7">
-        <v>2304</v>
+        <v>453</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåninggårdsvej 34</t>
+          <t xml:space="preserve">Lynæs Havnevej 13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2279835</t>
+          <t xml:space="preserve">719006, 2293825</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynæs Havnevej 3A</t>
+          <t xml:space="preserve">Lynæs Havnevej 15B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293833</t>
+          <t xml:space="preserve">719015, 2293827</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbjergvej 1A</t>
+          <t xml:space="preserve">Lynæs Havnevej 3A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2296052</t>
+          <t xml:space="preserve">2293833</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>453</v>
+        <v>273</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bellisvej 43</t>
+          <t xml:space="preserve">Melbyvej 134</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3370</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298768</t>
+          <t xml:space="preserve">8613481</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H11">
-        <v>267</v>
+        <v>1791</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 14</t>
+          <t xml:space="preserve">Melbyvej 134A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3370</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5317091</t>
+          <t xml:space="preserve">8613481</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H12">
-        <v>348</v>
+        <v>451</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,17 +751,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syrevej 55A</t>
+          <t xml:space="preserve">Nørregade 87</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318215, 100190403</t>
+          <t xml:space="preserve">100584098</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="H13">
-        <v>612</v>
+        <v>831</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krudtværksalleen 13</t>
+          <t xml:space="preserve">Skovfogedlodden 5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318232</t>
+          <t xml:space="preserve">2278774</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H14">
-        <v>485</v>
+        <v>384</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krudtværksalleen 10</t>
+          <t xml:space="preserve">Skåninggårdsvej 34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318242</t>
+          <t xml:space="preserve">2279835</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H15">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syrevej 51B</t>
+          <t xml:space="preserve">Sportsvej 5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">718961, 9641311</t>
+          <t xml:space="preserve">2278974</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H16">
-        <v>706</v>
+        <v>2304</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynæs Havnevej 13</t>
+          <t xml:space="preserve">Sportsvej 5C</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">719006, 2293825</t>
+          <t xml:space="preserve">10185333</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H17">
-        <v>439</v>
+        <v>1918</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynæs Havnevej 15B</t>
+          <t xml:space="preserve">Sportsvej 7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">719015, 2293827</t>
+          <t xml:space="preserve">10185333</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18">
-        <v>251</v>
+        <v>1112</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 134A</t>
+          <t xml:space="preserve">Syrevej 51B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3370</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8613481</t>
+          <t xml:space="preserve">718961, 9641311</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>451</v>
+        <v>706</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 134</t>
+          <t xml:space="preserve">Syrevej 55A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3370</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8613481</t>
+          <t xml:space="preserve">5318215, 100190403</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>1791</v>
+        <v>612</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133771</t>
+          <t xml:space="preserve">311133770</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133771</t>
+          <t xml:space="preserve">311133772</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1471,30 +1471,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Melbyvej 150</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3370</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2297884</t>
+          <t xml:space="preserve">9724887</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H25">
-        <v>1224</v>
+        <v>331</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140672</t>
+          <t xml:space="preserve">311140790</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1546,11 +1546,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H26">
-        <v>337</v>
+        <v>1224</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,30 +1591,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 150</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3370</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9724887</t>
+          <t xml:space="preserve">2297884</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H27">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140790</t>
+          <t xml:space="preserve">311140672</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 87</t>
+          <t xml:space="preserve">Industrivej 17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,20 +1661,20 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295652</t>
+          <t xml:space="preserve">9162566</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>2396</v>
+        <v>274</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140987</t>
+          <t xml:space="preserve">311141202</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 85</t>
+          <t xml:space="preserve">Industrivej 19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,20 +1721,20 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295652</t>
+          <t xml:space="preserve">9162566</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H29">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311140987</t>
+          <t xml:space="preserve">311141205</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 87</t>
+          <t xml:space="preserve">Nørregade 85</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1786,11 +1786,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30">
-        <v>1111</v>
+        <v>520</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1846,11 +1846,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H31">
-        <v>1044</v>
+        <v>2396</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 17</t>
+          <t xml:space="preserve">Nørregade 87</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,20 +1901,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162566</t>
+          <t xml:space="preserve">2295652</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H32">
-        <v>274</v>
+        <v>1111</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141202</t>
+          <t xml:space="preserve">311140987</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 19</t>
+          <t xml:space="preserve">Nørregade 87</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,20 +1961,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162566</t>
+          <t xml:space="preserve">2295652</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H33">
-        <v>494</v>
+        <v>1044</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311141205</t>
+          <t xml:space="preserve">311140987</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 134A</t>
+          <t xml:space="preserve">Melbyvej 134</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2086,11 +2086,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H35">
-        <v>345</v>
+        <v>842</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2146,11 +2146,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>1518</v>
+        <v>345</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 134</t>
+          <t xml:space="preserve">Melbyvej 134A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2206,11 +2206,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H37">
-        <v>842</v>
+        <v>1518</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 134B</t>
+          <t xml:space="preserve">Melbyvej 134A</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2266,15 +2266,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H38">
-        <v>1424</v>
+        <v>342</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143453</t>
+          <t xml:space="preserve">311143454</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbyvej 134A</t>
+          <t xml:space="preserve">Melbyvej 134B</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2326,15 +2326,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H39">
-        <v>342</v>
+        <v>1424</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143454</t>
+          <t xml:space="preserve">311143453</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11B</t>
+          <t xml:space="preserve">Højbjerggårdsvej 1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7807845</t>
+          <t xml:space="preserve">8727345</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,11 +2450,11 @@
         </is>
       </c>
       <c r="H41">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372721</t>
+          <t xml:space="preserve">311372706</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbjerggårdsvej 1</t>
+          <t xml:space="preserve">Nørregade 11B</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727345</t>
+          <t xml:space="preserve">7807845</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,11 +2510,11 @@
         </is>
       </c>
       <c r="H42">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372706</t>
+          <t xml:space="preserve">311372721</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølstedvej 24</t>
+          <t xml:space="preserve">Hovedgaden 2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562604</t>
+          <t xml:space="preserve">9122632</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,11 +2990,11 @@
         </is>
       </c>
       <c r="H50">
-        <v>685</v>
+        <v>5573</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718496</t>
+          <t xml:space="preserve">311718453</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 2</t>
+          <t xml:space="preserve">Ølstedvej 24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9122632</t>
+          <t xml:space="preserve">8562604</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,11 +3050,11 @@
         </is>
       </c>
       <c r="H51">
-        <v>5573</v>
+        <v>685</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718453</t>
+          <t xml:space="preserve">311718496</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlsgavevej 1</t>
+          <t xml:space="preserve">Bavnager 1A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3310</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278774</t>
+          <t xml:space="preserve">9773051</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,11 +3590,11 @@
         </is>
       </c>
       <c r="H60">
-        <v>7950</v>
+        <v>2154</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780833</t>
+          <t xml:space="preserve">311780838</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3631,17 +3631,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhjemsvej 7</t>
+          <t xml:space="preserve">Karlsgavevej 1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3370</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2287251</t>
+          <t xml:space="preserve">2278774</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,11 +3650,11 @@
         </is>
       </c>
       <c r="H61">
-        <v>3030</v>
+        <v>7950</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780834</t>
+          <t xml:space="preserve">311780833</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klokkedybet 2</t>
+          <t xml:space="preserve">Klokkedybet 12</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klokkedybet 12</t>
+          <t xml:space="preserve">Klokkedybet 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnager 1A</t>
+          <t xml:space="preserve">Solhjemsvej 7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310</t>
+          <t xml:space="preserve">3370</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9773051</t>
+          <t xml:space="preserve">2287251</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,11 +4010,11 @@
         </is>
       </c>
       <c r="H67">
-        <v>2154</v>
+        <v>3030</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780838</t>
+          <t xml:space="preserve">311780834</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstesvinget 3</t>
+          <t xml:space="preserve">Ahornvej 1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">100012416</t>
+          <t xml:space="preserve">5318273</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,11 +4070,11 @@
         </is>
       </c>
       <c r="H68">
-        <v>1337</v>
+        <v>635</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796292</t>
+          <t xml:space="preserve">311796294</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,30 +4111,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krudtværksvej 3</t>
+          <t xml:space="preserve">Birkevej 10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100034041</t>
+          <t xml:space="preserve">2295665</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H69">
-        <v>2033</v>
+        <v>411</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796290</t>
+          <t xml:space="preserve">311796287</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 47</t>
+          <t xml:space="preserve">Birkevej 10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,20 +4181,20 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290583</t>
+          <t xml:space="preserve">2295665</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H70">
-        <v>254</v>
+        <v>1601</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796289</t>
+          <t xml:space="preserve">311796286</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,30 +4231,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 10</t>
+          <t xml:space="preserve">Gjethusgade 5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295665</t>
+          <t xml:space="preserve">5317131</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>411</v>
+        <v>2198</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796287</t>
+          <t xml:space="preserve">311796293</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4291,30 +4291,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 10</t>
+          <t xml:space="preserve">Hovedgaden 25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3310</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295665</t>
+          <t xml:space="preserve">2300534</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H72">
-        <v>1601</v>
+        <v>694</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796286</t>
+          <t xml:space="preserve">311796281</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 25</t>
+          <t xml:space="preserve">Krudtværksalleen 7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300534</t>
+          <t xml:space="preserve">5318229</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,11 +4370,11 @@
         </is>
       </c>
       <c r="H73">
-        <v>694</v>
+        <v>325</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796281</t>
+          <t xml:space="preserve">311796291</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gjethusgade 5</t>
+          <t xml:space="preserve">Krudtværksvej 3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5317131</t>
+          <t xml:space="preserve">100034041</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,11 +4430,11 @@
         </is>
       </c>
       <c r="H74">
-        <v>2198</v>
+        <v>2033</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796293</t>
+          <t xml:space="preserve">311796290</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vognmandsgade 12</t>
+          <t xml:space="preserve">Præstesvinget 3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5317134</t>
+          <t xml:space="preserve">100012416</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="H75">
-        <v>582</v>
+        <v>1337</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796296</t>
+          <t xml:space="preserve">311796292</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,30 +4531,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vognmandsgade 14</t>
+          <t xml:space="preserve">Spodsbjergvej 4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5317134</t>
+          <t xml:space="preserve">8261705</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>452</v>
+        <v>1025</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796296</t>
+          <t xml:space="preserve">311796282</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krudtværksalleen 7</t>
+          <t xml:space="preserve">Strandvejen 47</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318229</t>
+          <t xml:space="preserve">2290583</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,11 +4610,11 @@
         </is>
       </c>
       <c r="H77">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796291</t>
+          <t xml:space="preserve">311796289</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 1</t>
+          <t xml:space="preserve">Vognmandsgade 12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318273</t>
+          <t xml:space="preserve">5317134</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,11 +4670,11 @@
         </is>
       </c>
       <c r="H78">
-        <v>635</v>
+        <v>582</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796294</t>
+          <t xml:space="preserve">311796296</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4711,30 +4711,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spodsbjergvej 4</t>
+          <t xml:space="preserve">Vognmandsgade 14</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261705</t>
+          <t xml:space="preserve">5317134</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H79">
-        <v>1025</v>
+        <v>452</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796282</t>
+          <t xml:space="preserve">311796296</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovfogedlodden 10</t>
+          <t xml:space="preserve">Baggersvej 17</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2278775</t>
+          <t xml:space="preserve">2298882</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,11 +4790,11 @@
         </is>
       </c>
       <c r="H80">
-        <v>702</v>
+        <v>920</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803332</t>
+          <t xml:space="preserve">311803329</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skåninggårdsvej 32</t>
+          <t xml:space="preserve">Birkedommeralle 6A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,20 +4841,20 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2279835</t>
+          <t xml:space="preserve">5318254</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>722</v>
+        <v>2110</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803330</t>
+          <t xml:space="preserve">311803335</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 61</t>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290025</t>
+          <t xml:space="preserve">2296052</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,11 +4910,11 @@
         </is>
       </c>
       <c r="H82">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803323</t>
+          <t xml:space="preserve">311803328</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 61</t>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,20 +4961,20 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290025</t>
+          <t xml:space="preserve">2296052</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H83">
-        <v>672</v>
+        <v>3658</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803323</t>
+          <t xml:space="preserve">311803328</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tømrergade 3</t>
+          <t xml:space="preserve">Lerbjergvej 1B</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,20 +5021,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290025</t>
+          <t xml:space="preserve">2296052</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H84">
-        <v>594</v>
+        <v>1012</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803337</t>
+          <t xml:space="preserve">311803328</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5086,11 +5086,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H85">
-        <v>792</v>
+        <v>1012</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5146,15 +5146,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H86">
-        <v>3658</v>
+        <v>1629</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803328</t>
+          <t xml:space="preserve">311803327</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbjergvej 1B</t>
+          <t xml:space="preserve">Nørregade 61</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,20 +5201,20 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2296052</t>
+          <t xml:space="preserve">2290025</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>1012</v>
+        <v>807</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803328</t>
+          <t xml:space="preserve">311803323</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbjergvej 1B</t>
+          <t xml:space="preserve">Nørregade 61</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,20 +5261,20 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2296052</t>
+          <t xml:space="preserve">2290025</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H88">
-        <v>1012</v>
+        <v>672</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803328</t>
+          <t xml:space="preserve">311803323</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5311,30 +5311,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbjergvej 1B</t>
+          <t xml:space="preserve">Skovfogedlodden 10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2296052</t>
+          <t xml:space="preserve">2278775</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>1629</v>
+        <v>702</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803327</t>
+          <t xml:space="preserve">311803332</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baggersvej 17</t>
+          <t xml:space="preserve">Skåninggårdsvej 32</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,20 +5381,20 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298882</t>
+          <t xml:space="preserve">2279835</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H90">
-        <v>920</v>
+        <v>722</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803329</t>
+          <t xml:space="preserve">311803330</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5551,30 +5551,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkedommeralle 6A</t>
+          <t xml:space="preserve">Tømrergade 3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3390</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5318254</t>
+          <t xml:space="preserve">2290025</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H93">
-        <v>2110</v>
+        <v>594</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803335</t>
+          <t xml:space="preserve">311803337</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnasvej 4</t>
+          <t xml:space="preserve">Baggersvej 19A</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3360</t>
+          <t xml:space="preserve">3300</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2284212</t>
+          <t xml:space="preserve">2298265</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,11 +5930,11 @@
         </is>
       </c>
       <c r="H99">
-        <v>538</v>
+        <v>644</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869855</t>
+          <t xml:space="preserve">311869857</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baggersvej 19A</t>
+          <t xml:space="preserve">Hovedgaden 1A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300</t>
+          <t xml:space="preserve">3310</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298265</t>
+          <t xml:space="preserve">2300568</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,11 +5990,11 @@
         </is>
       </c>
       <c r="H100">
-        <v>644</v>
+        <v>472</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869857</t>
+          <t xml:space="preserve">311869854</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 1A</t>
+          <t xml:space="preserve">Jonnasvej 4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310</t>
+          <t xml:space="preserve">3360</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300568</t>
+          <t xml:space="preserve">2284212</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,11 +6050,11 @@
         </is>
       </c>
       <c r="H101">
-        <v>472</v>
+        <v>538</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869854</t>
+          <t xml:space="preserve">311869855</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">

--- a/public/exports/29188416.xlsx
+++ b/public/exports/29188416.xlsx
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133772</t>
+          <t xml:space="preserve">311133771</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">

--- a/public/exports/29188416.xlsx
+++ b/public/exports/29188416.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:M106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevang Tegnestue</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-01-19</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-13</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1374,20 +1484,25 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133770</t>
+          <t xml:space="preserve">311133771</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1434,20 +1549,25 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133771</t>
+          <t xml:space="preserve">311133772</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-09</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-19</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-21</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-10-28</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevang Tegnestue</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-01</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-24</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-24</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-05</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-18</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-30</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-07</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-02</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-08</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,21 +6884,26 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L106"/>
+  <autoFilter ref="A1:M106"/>
 </worksheet>
 </file>
--- a/public/exports/29188416.xlsx
+++ b/public/exports/29188416.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133771</t>
+          <t xml:space="preserve">311133770</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311133772</t>
+          <t xml:space="preserve">311133771</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
